--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2109-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2109-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CDB48E9-5693-4CE0-BF2D-15F03EC78A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3AF8883-FA5E-4B70-93C2-A3D7778085B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{1F1161E2-9A26-4364-939E-F76D4F9977CB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{33B48B10-AEEA-4E71-8BCC-FDC89A5F4014}"/>
   </bookViews>
   <sheets>
     <sheet name="2109-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1490,27 +1490,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D04F965-E6C1-404A-9F28-715F0961ACF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFC0A29B-C7B2-421F-AD1B-C14FAFCE7879}">
   <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="6.75" customWidth="1"/>
-    <col min="7" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="5.88671875" customWidth="1"/>
+    <col min="7" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1544,7 +1544,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1580,7 +1580,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1700,7 +1700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2021</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>8.07</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2020</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2019</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2018</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2017</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2016</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2015</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2014</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2013</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2012</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2011</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2010</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2009</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2008</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2007</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2006</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2005</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2004</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2003</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2002</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2001</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2000</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>1999</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1998</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>1997</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>1996</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>1995</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>1994</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>1993</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>1992</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <v>1991</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>1990</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
         <v>1988</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="37">
         <v>1982</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
         <v>1980</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="37">
         <v>1978</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="35">
         <v>1975</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="37" t="s">
         <v>51</v>
       </c>
